--- a/graph.xlsx
+++ b/graph.xlsx
@@ -5,27 +5,36 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DeepFake-pjt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB3FB34-95CB-4BF1-A5A4-23AC985CFF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535D6520-E273-4F6A-93C5-331F386D9A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>epoch</t>
   </si>
@@ -41,12 +50,33 @@
   <si>
     <t>loss</t>
   </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>frames</t>
+  </si>
+  <si>
+    <t>SSIM</t>
+  </si>
+  <si>
+    <t>PSNR</t>
+  </si>
+  <si>
+    <t>watermark1</t>
+  </si>
+  <si>
+    <t>watermark2</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,6 +101,23 @@
       <color theme="1"/>
       <name val="Var(--jp-code-font-family)"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -92,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -100,6 +147,11 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3527,7 +3579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:C118"/>
+  <dimension ref="A5:N118"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="5" spans="1:3">
@@ -4091,7 +4143,8 @@
         <v>0.65129999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="66" spans="1:14" ht="18.5" customHeight="1"/>
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
         <v>0</v>
       </c>
@@ -4101,320 +4154,811 @@
       <c r="C67" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="I67" t="s">
+        <v>5</v>
+      </c>
+      <c r="J67" t="s">
+        <v>6</v>
+      </c>
+      <c r="K67" t="s">
+        <v>7</v>
+      </c>
+      <c r="L67" t="s">
+        <v>8</v>
+      </c>
+      <c r="M67" t="s">
+        <v>9</v>
+      </c>
+      <c r="N67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68">
         <v>1</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="5">
         <v>0.5</v>
       </c>
       <c r="C68" s="3">
         <v>0.68200000000000005</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>469</v>
+      </c>
+      <c r="K68" s="7">
+        <v>0.95863900000000002</v>
+      </c>
+      <c r="L68" s="7">
+        <v>38.501600000000003</v>
+      </c>
+      <c r="M68" s="7">
+        <v>0.79779999999999995</v>
+      </c>
+      <c r="N68" s="7">
+        <v>0.99629999999999996</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69">
         <v>2</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="6">
         <v>0.5</v>
       </c>
       <c r="C69" s="3">
         <v>0.36009999999999998</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69" s="3">
+        <v>372</v>
+      </c>
+      <c r="K69" s="7">
+        <v>0.99348000000000003</v>
+      </c>
+      <c r="L69" s="7">
+        <v>42.501899999999999</v>
+      </c>
+      <c r="M69" s="7">
+        <v>0.68049999999999999</v>
+      </c>
+      <c r="N69" s="7">
+        <v>0.99460000000000004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70">
         <v>3</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="6">
         <v>0.5</v>
       </c>
       <c r="C70" s="3">
         <v>0.3488</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="I70">
+        <v>3</v>
+      </c>
+      <c r="J70" s="3">
+        <v>450</v>
+      </c>
+      <c r="K70" s="7">
+        <v>0.98623700000000003</v>
+      </c>
+      <c r="L70" s="7">
+        <v>39.206099999999999</v>
+      </c>
+      <c r="M70" s="7">
+        <v>0.8518</v>
+      </c>
+      <c r="N70" s="7">
+        <v>0.99580000000000002</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71">
         <v>4</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="6">
         <v>1</v>
       </c>
       <c r="C71" s="3">
         <v>0.34449999999999997</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="I71">
+        <v>4</v>
+      </c>
+      <c r="J71" s="3">
+        <v>512</v>
+      </c>
+      <c r="K71" s="7">
+        <v>0.98738999999999999</v>
+      </c>
+      <c r="L71" s="7">
+        <v>40.625300000000003</v>
+      </c>
+      <c r="M71" s="7">
+        <v>0.81679999999999997</v>
+      </c>
+      <c r="N71" s="7">
+        <v>0.99570000000000003</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72">
         <v>5</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="6">
         <v>1</v>
       </c>
       <c r="C72" s="3">
         <v>0.34139999999999998</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="I72">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
+        <v>415</v>
+      </c>
+      <c r="K72" s="7">
+        <v>0.95900399999999997</v>
+      </c>
+      <c r="L72" s="7">
+        <v>38.898299999999999</v>
+      </c>
+      <c r="M72" s="7">
+        <v>0.80479999999999996</v>
+      </c>
+      <c r="N72" s="7">
+        <v>0.99560000000000004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73">
         <v>6</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="6">
         <v>1</v>
       </c>
       <c r="C73" s="3">
         <v>0.33489999999999998</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="I73">
+        <v>6</v>
+      </c>
+      <c r="J73" s="3">
+        <v>295</v>
+      </c>
+      <c r="K73" s="7">
+        <v>0.99165800000000004</v>
+      </c>
+      <c r="L73" s="7">
+        <v>41.044699999999999</v>
+      </c>
+      <c r="M73" s="7">
+        <v>0.79120000000000001</v>
+      </c>
+      <c r="N73" s="7">
+        <v>0.99590000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74">
         <v>7</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="6">
         <v>1</v>
       </c>
       <c r="C74" s="3">
         <v>0.32450000000000001</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="I74">
+        <v>7</v>
+      </c>
+      <c r="J74" s="3">
+        <v>450</v>
+      </c>
+      <c r="K74" s="7">
+        <v>0.99336999999999998</v>
+      </c>
+      <c r="L74" s="7">
+        <v>41.981900000000003</v>
+      </c>
+      <c r="M74" s="7">
+        <v>0.64470000000000005</v>
+      </c>
+      <c r="N74" s="7">
+        <v>0.99450000000000005</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75">
         <v>8</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="6">
         <v>1</v>
       </c>
       <c r="C75" s="3">
         <v>0.30990000000000001</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="I75">
+        <v>8</v>
+      </c>
+      <c r="J75" s="3">
+        <v>486</v>
+      </c>
+      <c r="K75" s="7">
+        <v>0.97501199999999999</v>
+      </c>
+      <c r="L75" s="7">
+        <v>41.671100000000003</v>
+      </c>
+      <c r="M75" s="7">
+        <v>0.74209999999999998</v>
+      </c>
+      <c r="N75" s="7">
+        <v>0.99319999999999997</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76">
         <v>9</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="6">
         <v>1</v>
       </c>
       <c r="C76" s="3">
         <v>0.29099999999999998</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="I76">
+        <v>9</v>
+      </c>
+      <c r="J76" s="3">
+        <v>463</v>
+      </c>
+      <c r="K76" s="7">
+        <v>0.99187899999999996</v>
+      </c>
+      <c r="L76" s="7">
+        <v>41.715699999999998</v>
+      </c>
+      <c r="M76" s="7">
+        <v>0.7329</v>
+      </c>
+      <c r="N76" s="7">
+        <v>0.9829</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77">
         <v>10</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="6">
         <v>1</v>
       </c>
       <c r="C77" s="3">
         <v>0.26800000000000002</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="I77">
+        <v>10</v>
+      </c>
+      <c r="J77" s="3">
+        <v>474</v>
+      </c>
+      <c r="K77" s="7">
+        <v>0.97256900000000002</v>
+      </c>
+      <c r="L77" s="7">
+        <v>39.176099999999998</v>
+      </c>
+      <c r="M77" s="7">
+        <v>0.89029999999999998</v>
+      </c>
+      <c r="N77" s="7">
+        <v>0.99229999999999996</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78">
         <v>11</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="6">
         <v>1</v>
       </c>
       <c r="C78" s="3">
         <v>0.24149999999999999</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="I78">
+        <v>11</v>
+      </c>
+      <c r="J78" s="3">
+        <v>477</v>
+      </c>
+      <c r="K78" s="7">
+        <v>0.99351699999999998</v>
+      </c>
+      <c r="L78" s="7">
+        <v>37.768300000000004</v>
+      </c>
+      <c r="M78" s="7">
+        <v>0.87229999999999996</v>
+      </c>
+      <c r="N78" s="7">
+        <v>0.99399999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79">
         <v>12</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="6">
         <v>1</v>
       </c>
       <c r="C79" s="3">
         <v>0.21199999999999999</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="I79">
+        <v>12</v>
+      </c>
+      <c r="J79" s="3">
+        <v>575</v>
+      </c>
+      <c r="K79" s="7">
+        <v>0.98970000000000002</v>
+      </c>
+      <c r="L79" s="7">
+        <v>38.754800000000003</v>
+      </c>
+      <c r="M79" s="7">
+        <v>0.87139999999999995</v>
+      </c>
+      <c r="N79" s="7">
+        <v>0.99590000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80">
         <v>13</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="6">
         <v>1</v>
       </c>
       <c r="C80" s="3">
         <v>0.18090000000000001</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="I80">
+        <v>13</v>
+      </c>
+      <c r="J80" s="3">
+        <v>470</v>
+      </c>
+      <c r="K80" s="7">
+        <v>0.93311200000000005</v>
+      </c>
+      <c r="L80" s="7">
+        <v>39.328099999999999</v>
+      </c>
+      <c r="M80" s="7">
+        <v>0.87290000000000001</v>
+      </c>
+      <c r="N80" s="7">
+        <v>0.99580000000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81">
         <v>14</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="6">
         <v>1</v>
       </c>
       <c r="C81" s="3">
         <v>0.14940000000000001</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="I81">
+        <v>14</v>
+      </c>
+      <c r="J81" s="3">
+        <v>422</v>
+      </c>
+      <c r="K81" s="7">
+        <v>0.99600999999999995</v>
+      </c>
+      <c r="L81" s="7">
+        <v>40.985700000000001</v>
+      </c>
+      <c r="M81" s="7">
+        <v>0.90910000000000002</v>
+      </c>
+      <c r="N81" s="7">
+        <v>0.99650000000000005</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82">
         <v>15</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="6">
         <v>1</v>
       </c>
       <c r="C82" s="3">
         <v>0.1191</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="I82">
+        <v>15</v>
+      </c>
+      <c r="J82" s="3">
+        <v>474</v>
+      </c>
+      <c r="K82" s="7">
+        <v>0.97899099999999994</v>
+      </c>
+      <c r="L82" s="7">
+        <v>40.206600000000002</v>
+      </c>
+      <c r="M82" s="7">
+        <v>0.83520000000000005</v>
+      </c>
+      <c r="N82" s="7">
+        <v>0.99580000000000002</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83">
         <v>16</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="6">
         <v>1</v>
       </c>
       <c r="C83" s="3">
         <v>9.1499999999999998E-2</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="I83">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3">
+        <v>397</v>
+      </c>
+      <c r="K83" s="7">
+        <v>0.98151500000000003</v>
+      </c>
+      <c r="L83" s="7">
+        <v>38.122199999999999</v>
+      </c>
+      <c r="M83" s="7">
+        <v>0.85509999999999997</v>
+      </c>
+      <c r="N83" s="7">
+        <v>0.99639999999999995</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84">
         <v>17</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="6">
         <v>1</v>
       </c>
       <c r="C84" s="3">
         <v>6.7699999999999996E-2</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="I84">
+        <v>17</v>
+      </c>
+      <c r="J84" s="3">
+        <v>442</v>
+      </c>
+      <c r="K84" s="7">
+        <v>0.99374799999999996</v>
+      </c>
+      <c r="L84" s="7">
+        <v>39.538499999999999</v>
+      </c>
+      <c r="M84" s="7">
+        <v>0.82150000000000001</v>
+      </c>
+      <c r="N84" s="7">
+        <v>0.99390000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85">
         <v>18</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="6">
         <v>1</v>
       </c>
       <c r="C85" s="3">
         <v>4.8399999999999999E-2</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="I85">
+        <v>18</v>
+      </c>
+      <c r="J85" s="3">
+        <v>461</v>
+      </c>
+      <c r="K85" s="7">
+        <v>0.988958</v>
+      </c>
+      <c r="L85" s="7">
+        <v>40.974600000000002</v>
+      </c>
+      <c r="M85" s="7">
+        <v>0.83989999999999998</v>
+      </c>
+      <c r="N85" s="7">
+        <v>0.99050000000000005</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86">
         <v>19</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="6">
         <v>1</v>
       </c>
       <c r="C86" s="3">
         <v>3.3599999999999998E-2</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="I86">
+        <v>19</v>
+      </c>
+      <c r="J86" s="3">
+        <v>319</v>
+      </c>
+      <c r="K86" s="7">
+        <v>0.99617900000000004</v>
+      </c>
+      <c r="L86" s="7">
+        <v>40.336599999999997</v>
+      </c>
+      <c r="M86" s="7">
+        <v>0.81269999999999998</v>
+      </c>
+      <c r="N86" s="7">
+        <v>0.99509999999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87">
         <v>20</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="6">
         <v>1</v>
       </c>
       <c r="C87" s="3">
         <v>2.2800000000000001E-2</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="I87">
+        <v>20</v>
+      </c>
+      <c r="J87" s="3">
+        <v>282</v>
+      </c>
+      <c r="K87" s="7">
+        <v>0.972862</v>
+      </c>
+      <c r="L87" s="7">
+        <v>38.488599999999998</v>
+      </c>
+      <c r="M87" s="7">
+        <v>0.70889999999999997</v>
+      </c>
+      <c r="N87" s="7">
+        <v>0.99590000000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88">
         <v>21</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="6">
         <v>1</v>
       </c>
       <c r="C88" s="3">
         <v>1.52E-2</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="I88">
+        <v>21</v>
+      </c>
+      <c r="J88" s="7">
+        <v>316</v>
+      </c>
+      <c r="K88" s="7">
+        <v>0.99426400000000004</v>
+      </c>
+      <c r="L88" s="7">
+        <v>41.608499999999999</v>
+      </c>
+      <c r="M88" s="7">
+        <v>0.72989999999999999</v>
+      </c>
+      <c r="N88" s="7">
+        <v>0.99039999999999995</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89">
         <v>22</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="6">
         <v>1</v>
       </c>
       <c r="C89" s="3">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="I89">
+        <v>22</v>
+      </c>
+      <c r="J89" s="7">
+        <v>363</v>
+      </c>
+      <c r="K89" s="7">
+        <v>0.994232</v>
+      </c>
+      <c r="L89" s="7">
+        <v>41.636899999999997</v>
+      </c>
+      <c r="M89" s="7">
+        <v>0.7288</v>
+      </c>
+      <c r="N89" s="7">
+        <v>0.99119999999999997</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90">
         <v>23</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="6">
         <v>1</v>
       </c>
       <c r="C90" s="3">
         <v>6.6E-3</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="I90">
+        <v>23</v>
+      </c>
+      <c r="J90" s="3">
+        <v>303</v>
+      </c>
+      <c r="K90" s="7">
+        <v>0.97355700000000001</v>
+      </c>
+      <c r="L90" s="7">
+        <v>40.14</v>
+      </c>
+      <c r="M90" s="7">
+        <v>0.86919999999999997</v>
+      </c>
+      <c r="N90" s="7">
+        <v>0.99560000000000004</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91">
         <v>24</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="6">
         <v>1</v>
       </c>
       <c r="C91" s="3">
         <v>4.4000000000000003E-3</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="I91">
+        <v>24</v>
+      </c>
+      <c r="J91" s="3">
+        <v>410</v>
+      </c>
+      <c r="K91" s="7">
+        <v>0.98496099999999998</v>
+      </c>
+      <c r="L91" s="7">
+        <v>39.567799999999998</v>
+      </c>
+      <c r="M91" s="7">
+        <v>0.80789999999999995</v>
+      </c>
+      <c r="N91" s="7">
+        <v>0.99560000000000004</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92">
         <v>25</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="6">
         <v>1</v>
       </c>
       <c r="C92" s="3">
         <v>2.8999999999999998E-3</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="I92">
+        <v>25</v>
+      </c>
+      <c r="J92" s="3">
+        <v>345</v>
+      </c>
+      <c r="K92" s="7">
+        <v>0.995259</v>
+      </c>
+      <c r="L92" s="7">
+        <v>42.389099999999999</v>
+      </c>
+      <c r="M92" s="7">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="N92" s="7">
+        <v>0.9919</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93">
         <v>26</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="6">
         <v>1</v>
       </c>
       <c r="C93" s="3">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="I93" t="s">
+        <v>11</v>
+      </c>
+      <c r="J93">
+        <f>SUM(J68:J92)</f>
+        <v>10442</v>
+      </c>
+      <c r="K93">
+        <f>AVERAGE(K68:K92)</f>
+        <v>0.98304411999999997</v>
+      </c>
+      <c r="L93">
+        <f>AVERAGE(L68:L92)</f>
+        <v>40.206760000000003</v>
+      </c>
+      <c r="M93">
+        <f>AVERAGE(M68:M92)</f>
+        <v>0.79226799999999997</v>
+      </c>
+      <c r="N93">
+        <f>AVERAGE(N68:N92)</f>
+        <v>0.99405199999999994</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94">
         <v>27</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="6">
         <v>1</v>
       </c>
       <c r="C94" s="3">
         <v>1.4E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:14">
       <c r="A95">
         <v>28</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="6">
         <v>1</v>
       </c>
       <c r="C95" s="4">
         <v>9.6973999999999997E-4</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:14">
       <c r="A96">
         <v>29</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="6">
         <v>1</v>
       </c>
       <c r="C96" s="4">
@@ -4425,7 +4969,7 @@
       <c r="A97">
         <v>30</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="6">
         <v>1</v>
       </c>
       <c r="C97" s="4">
@@ -4436,7 +4980,7 @@
       <c r="A98">
         <v>31</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98" s="6">
         <v>1</v>
       </c>
       <c r="C98" s="4">
@@ -4447,7 +4991,7 @@
       <c r="A99">
         <v>32</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99" s="6">
         <v>1</v>
       </c>
       <c r="C99" s="4">
@@ -4458,7 +5002,7 @@
       <c r="A100">
         <v>33</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100" s="6">
         <v>1</v>
       </c>
       <c r="C100" s="4">
@@ -4469,7 +5013,7 @@
       <c r="A101">
         <v>34</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101" s="6">
         <v>1</v>
       </c>
       <c r="C101" s="4">
@@ -4480,7 +5024,7 @@
       <c r="A102">
         <v>35</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B102" s="6">
         <v>1</v>
       </c>
       <c r="C102" s="4">
@@ -4491,7 +5035,7 @@
       <c r="A103">
         <v>36</v>
       </c>
-      <c r="B103" s="1">
+      <c r="B103" s="6">
         <v>1</v>
       </c>
       <c r="C103" s="4">
@@ -4502,7 +5046,7 @@
       <c r="A104">
         <v>37</v>
       </c>
-      <c r="B104" s="1">
+      <c r="B104" s="6">
         <v>1</v>
       </c>
       <c r="C104" s="4">
@@ -4513,7 +5057,7 @@
       <c r="A105">
         <v>38</v>
       </c>
-      <c r="B105" s="1">
+      <c r="B105" s="6">
         <v>1</v>
       </c>
       <c r="C105" s="4">
@@ -4524,7 +5068,7 @@
       <c r="A106">
         <v>39</v>
       </c>
-      <c r="B106" s="1">
+      <c r="B106" s="6">
         <v>1</v>
       </c>
       <c r="C106" s="4">
@@ -4535,7 +5079,7 @@
       <c r="A107">
         <v>40</v>
       </c>
-      <c r="B107" s="1">
+      <c r="B107" s="6">
         <v>1</v>
       </c>
       <c r="C107" s="4">
@@ -4546,7 +5090,7 @@
       <c r="A108">
         <v>41</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108" s="6">
         <v>1</v>
       </c>
       <c r="C108" s="4">
@@ -4557,7 +5101,7 @@
       <c r="A109">
         <v>42</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B109" s="6">
         <v>1</v>
       </c>
       <c r="C109" s="4">
@@ -4568,7 +5112,7 @@
       <c r="A110">
         <v>43</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110" s="6">
         <v>1</v>
       </c>
       <c r="C110" s="4">
@@ -4579,7 +5123,7 @@
       <c r="A111">
         <v>44</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B111" s="6">
         <v>1</v>
       </c>
       <c r="C111" s="4">
@@ -4590,7 +5134,7 @@
       <c r="A112">
         <v>45</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112" s="6">
         <v>1</v>
       </c>
       <c r="C112" s="4">
@@ -4601,7 +5145,7 @@
       <c r="A113">
         <v>46</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113" s="6">
         <v>1</v>
       </c>
       <c r="C113" s="4">
@@ -4612,7 +5156,7 @@
       <c r="A114">
         <v>47</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114" s="6">
         <v>1</v>
       </c>
       <c r="C114" s="4">
@@ -4623,7 +5167,7 @@
       <c r="A115">
         <v>48</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115" s="6">
         <v>1</v>
       </c>
       <c r="C115" s="4">
@@ -4634,7 +5178,7 @@
       <c r="A116">
         <v>49</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116" s="6">
         <v>1</v>
       </c>
       <c r="C116" s="4">
@@ -4645,7 +5189,7 @@
       <c r="A117">
         <v>50</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117" s="6">
         <v>1</v>
       </c>
       <c r="C117" s="4">
@@ -4653,9 +5197,7 @@
       </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="B118" s="1">
-        <v>1</v>
-      </c>
+      <c r="B118" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
